--- a/app/www/profiles/profile-Wine-noesy-500.xlsx
+++ b/app/www/profiles/profile-Wine-noesy-500.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\WAP-NMR\Manips\URO_RMN_500\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15164EDE-0CE1-4E0E-9D62-E1E8DAD3F719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1106B7A5-6CFC-49F3-B00C-1FD1D9CC4327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="1500" windowWidth="18036" windowHeight="10452" xr2:uid="{E36E621C-9921-4C41-8902-EB76B5BFB8E7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11235" xr2:uid="{E36E621C-9921-4C41-8902-EB76B5BFB8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="profile-Wine-noesy-500" sheetId="1" r:id="rId1"/>
@@ -265,9 +265,6 @@
     <t>3,3,0.4</t>
   </si>
   <si>
-    <t>3,6,0.5,120</t>
-  </si>
-  <si>
     <t>5.209,5.2165,0,10,0.6,150</t>
   </si>
   <si>
@@ -278,6 +275,9 @@
   </si>
   <si>
     <t>5.305,5.313,0,2,0.5,150</t>
+  </si>
+  <si>
+    <t>4.617,4.64,0,6,0.5,150</t>
   </si>
 </sst>
 </file>
@@ -1140,16 +1140,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65860E65-6B51-4E73-B766-AFF1587EA751}">
   <dimension ref="A1:K77"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>75</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>0</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>7.1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>78</v>
@@ -2115,7 +2115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H35" s="1">
         <v>6</v>
@@ -2150,7 +2150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>43</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1">
         <v>4.6210000000000004</v>
@@ -2167,7 +2167,7 @@
         <v>7.9</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>44</v>
@@ -2185,7 +2185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>3.6</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>3.8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>76</v>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>27</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>27</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>73</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>0</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>88.147999999999996</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>19</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>60.052</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>19</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>180.1559</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>19</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>180.1559</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>19</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>180.1574</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>19</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>290.2681</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>19</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>290.2681</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>19</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>88.11</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>19</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>118.13</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>180.15600000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>116.0722</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>19</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>194.13939999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>170.11949999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>134.0874</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>174.15</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>19</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>112.13</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>118.09</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>148.07</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>137.136</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>138.166</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>19</v>
       </c>

--- a/app/www/profiles/profile-Wine-noesy-500.xlsx
+++ b/app/www/profiles/profile-Wine-noesy-500.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\WAP-NMR\Manips\URO_RMN_500\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1106B7A5-6CFC-49F3-B00C-1FD1D9CC4327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D025F68-DA50-46F0-8B26-236C64013D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11235" xr2:uid="{E36E621C-9921-4C41-8902-EB76B5BFB8E7}"/>
+    <workbookView xWindow="-30840" yWindow="-1230" windowWidth="30960" windowHeight="15720" xr2:uid="{E36E621C-9921-4C41-8902-EB76B5BFB8E7}"/>
   </bookViews>
   <sheets>
     <sheet name="profile-Wine-noesy-500" sheetId="1" r:id="rId1"/>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1">
         <v>50</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I47" s="1">
         <v>1</v>
